--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487671_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487671_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>E. PASCUAL COZAR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4495</v>
+        <v>1.5539</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6867</v>
+        <v>4.222</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7628</v>
+        <v>-2.6682</v>
       </c>
       <c r="G2" t="n">
-        <v>1.0766</v>
+        <v>3.3851</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0471</v>
+        <v>0.4037</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0295</v>
+        <v>2.9813</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7944</v>
+        <v>5.4112</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4212</v>
+        <v>0.9228</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6267</v>
+        <v>4.4885</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2821</v>
+        <v>-2.0262</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.374</v>
+        <v>-0.5191</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6562</v>
+        <v>-1.5071</v>
       </c>
       <c r="P2" t="n">
-        <v>0.194</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1642</v>
+        <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>0.461</v>
+        <v>1.1987</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8625</v>
+        <v>0.7511</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4015</v>
+        <v>0.4475</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.2821</v>
+        <v>-2.4477</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2821</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. LAPASTORA ARACIL</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0941</v>
+        <v>0.8489</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3743</v>
+        <v>0.0862</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7198</v>
+        <v>0.7628</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.6038</v>
+        <v>1.0766</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.5738</v>
+        <v>1.0471</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03</v>
+        <v>0.0295</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.1003</v>
+        <v>0.7944</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.4253</v>
+        <v>1.4212</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.675</v>
+        <v>-0.6267</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5034</v>
+        <v>0.2821</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1485</v>
+        <v>-0.374</v>
       </c>
       <c r="O3" t="n">
-        <v>0.645</v>
+        <v>0.6562</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.194</v>
+        <v>0.194</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4441</v>
+        <v>-0.1396</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9672</v>
+        <v>0.2619</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5231</v>
+        <v>-0.4015</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4477</v>
+        <v>-0.2821</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. PASCUAL COZAR</t>
+          <t>J. LAPASTORA ARACIL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9265</v>
+        <v>0.7115</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9217</v>
+        <v>-0.2263</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.9952</v>
+        <v>0.9378</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3851</v>
+        <v>-2.6038</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4037</v>
+        <v>-2.5738</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9813</v>
+        <v>-0.03</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4112</v>
+        <v>-2.1003</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9228</v>
+        <v>-1.4253</v>
       </c>
       <c r="L4" t="n">
-        <v>4.4885</v>
+        <v>-0.675</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0262</v>
+        <v>-0.5034</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5191</v>
+        <v>-1.1485</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5071</v>
+        <v>0.645</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5821</v>
+        <v>-0.194</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3582</v>
+        <v>1.7463</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5713</v>
+        <v>1.0616</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4508</v>
+        <v>1.3666</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1205</v>
+        <v>-0.305</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.4477</v>
+        <v>2.4477</v>
       </c>
       <c r="W4" t="n">
+        <v>2.4477</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-2.4477</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. MANZANERO CAMACHO</t>
+          <t>N. LASUNCION MARIBLANCA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8253</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7616000000000001</v>
+        <v>1.2148</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0638</v>
+        <v>-1.3061</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.8935</v>
+        <v>0.9943</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8842</v>
+        <v>0.089</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0093</v>
+        <v>0.9053</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9889</v>
+        <v>3.4209</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4078</v>
+        <v>0.7415</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5810999999999999</v>
+        <v>2.6794</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9046</v>
+        <v>-2.4266</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4764</v>
+        <v>-0.6525</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4282</v>
+        <v>-1.774</v>
       </c>
       <c r="P5" t="n">
-        <v>0.194</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0188</v>
+        <v>0.5249</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2146</v>
+        <v>0.0925</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8042</v>
+        <v>0.4324</v>
       </c>
       <c r="V5" t="n">
-        <v>1.506</v>
+        <v>0.3299</v>
       </c>
       <c r="W5" t="n">
-        <v>1.506</v>
+        <v>0.6119</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GARCIA-LARRACHE SEGURA</t>
+          <t>D. MANZANERO CAMACHO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1659</v>
+        <v>-0.3843</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.6717</v>
+        <v>-0.0392</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5059</v>
+        <v>-0.3451</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3253</v>
+        <v>-2.8935</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0321</v>
+        <v>-1.8842</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3575</v>
+        <v>-1.0093</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.6138</v>
+        <v>-0.9889</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9516</v>
+        <v>-0.4078</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6623</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2885</v>
+        <v>-1.9046</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9837</v>
+        <v>-1.4764</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6952</v>
+        <v>-0.4282</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>1.849</v>
+        <v>0.8092</v>
       </c>
       <c r="T6" t="n">
-        <v>0.572</v>
+        <v>0.4138</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2771</v>
+        <v>0.3954</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2716</v>
+        <v>1.506</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6597</v>
+        <v>1.506</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANTOS</t>
+          <t>J. GARCIA-LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6582</v>
+        <v>-0.5291</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0791</v>
+        <v>-2.5716</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7373</v>
+        <v>2.0426</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4168</v>
+        <v>-1.3253</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008</v>
+        <v>0.0321</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4176</v>
+        <v>-1.3575</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0174</v>
+        <v>-1.6138</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.655</v>
+        <v>-0.9516</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6724</v>
+        <v>-0.6623</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4342</v>
+        <v>0.2885</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6558</v>
+        <v>0.9837</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.09</v>
+        <v>-0.6952</v>
       </c>
       <c r="P7" t="n">
         <v>0.5821</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5821</v>
+        <v>1.5523</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4004</v>
+        <v>1.4858</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0617</v>
+        <v>0.6721</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3387</v>
+        <v>0.8137</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2239</v>
+        <v>-1.2716</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2239</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. LASUNCION MARIBLANCA</t>
+          <t>J. MARTINEZ SANTOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2285</v>
+        <v>-0.7583</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2138</v>
+        <v>-0.021</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4424</v>
+        <v>-0.7373</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9943</v>
+        <v>-0.4168</v>
       </c>
       <c r="H8" t="n">
-        <v>0.089</v>
+        <v>0.0008</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9053</v>
+        <v>-0.4176</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4209</v>
+        <v>0.0174</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7415</v>
+        <v>-0.655</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6794</v>
+        <v>0.6724</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4266</v>
+        <v>-0.4342</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6525</v>
+        <v>0.6558</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.774</v>
+        <v>-1.09</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.9403</v>
+        <v>0.5821</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6124000000000001</v>
+        <v>0.3003</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9085</v>
+        <v>-0.0384</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2961</v>
+        <v>0.3387</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3299</v>
+        <v>-1.2239</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7679</v>
+        <v>-1.7868</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6348</v>
+        <v>-2.0352</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1331</v>
+        <v>0.2484</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4632</v>
@@ -1156,13 +1156,13 @@
         <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9475</v>
+        <v>0.9286</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3604</v>
+        <v>0.96</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.413</v>
+        <v>-0.0314</v>
       </c>
       <c r="V9" t="n">
         <v>0.3299</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0138</v>
+        <v>-1.8681</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0856</v>
+        <v>0.2858</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0993</v>
+        <v>-2.1538</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0257</v>
@@ -1234,13 +1234,13 @@
         <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0119</v>
+        <v>0.1576</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.12</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1319</v>
+        <v>0.0774</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2239</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3344</v>
+        <v>-3.5697</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6829</v>
+        <v>-3.782</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3485</v>
+        <v>0.2123</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0663</v>
@@ -1312,13 +1312,13 @@
         <v>1.5523</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.48</v>
+        <v>0.2846</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5933</v>
+        <v>0.3076</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1133</v>
+        <v>-0.023</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4</v>
@@ -1348,22 +1348,22 @@
         <v>-5.8733</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8666</v>
+        <v>-2.866499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.0065</v>
+        <v>-3.0066</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.3386</v>
+        <v>-5.338599999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.673400000000001</v>
+        <v>-6.6734</v>
       </c>
       <c r="I12" t="n">
         <v>1.3347</v>
       </c>
       <c r="J12" t="n">
-        <v>2.0469</v>
+        <v>2.046900000000001</v>
       </c>
       <c r="K12" t="n">
         <v>-3.5425</v>
@@ -1378,7 +1378,7 @@
         <v>-3.1309</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.2546</v>
+        <v>-4.254600000000001</v>
       </c>
       <c r="P12" t="n">
         <v>-2.9105</v>
@@ -1390,7 +1390,7 @@
         <v>12.6122</v>
       </c>
       <c r="S12" t="n">
-        <v>6.611600000000001</v>
+        <v>6.6117</v>
       </c>
       <c r="T12" t="n">
         <v>4.8674</v>
@@ -1402,7 +1402,7 @@
         <v>-4.2357</v>
       </c>
       <c r="W12" t="n">
-        <v>5.741700000000001</v>
+        <v>5.7417</v>
       </c>
       <c r="X12" t="n">
         <v>-9.977600000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0899</v>
+        <v>5.9931</v>
       </c>
       <c r="E13" t="n">
-        <v>1.681</v>
+        <v>1.4808</v>
       </c>
       <c r="F13" t="n">
-        <v>4.4089</v>
+        <v>4.5123</v>
       </c>
       <c r="G13" t="n">
         <v>3.6399</v>
@@ -1468,13 +1468,13 @@
         <v>2.7164</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6798999999999999</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0145</v>
+        <v>-0.1857</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6944</v>
+        <v>-0.591</v>
       </c>
       <c r="V13" t="n">
         <v>1.3836</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9324</v>
+        <v>3.6726</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5774</v>
+        <v>3.0779</v>
       </c>
       <c r="F14" t="n">
-        <v>0.355</v>
+        <v>0.5947</v>
       </c>
       <c r="G14" t="n">
         <v>3.0737</v>
@@ -1546,13 +1546,13 @@
         <v>1.5523</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.9473</v>
+        <v>-1.2071</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8356</v>
+        <v>-0.3351</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1117</v>
+        <v>-0.872</v>
       </c>
       <c r="V14" t="n">
         <v>1.2239</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8495</v>
+        <v>3.4896</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3472</v>
+        <v>4.7476</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4977</v>
+        <v>-1.2581</v>
       </c>
       <c r="G15" t="n">
         <v>4.09</v>
@@ -1624,13 +1624,13 @@
         <v>2.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1465</v>
+        <v>-0.5064</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7739</v>
+        <v>-0.3735</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3725</v>
+        <v>-0.1329</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0642</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7086</v>
+        <v>2.8449</v>
       </c>
       <c r="E16" t="n">
         <v>1.3803</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3284</v>
+        <v>1.4646</v>
       </c>
       <c r="G16" t="n">
         <v>1.1641</v>
@@ -1702,13 +1702,13 @@
         <v>1.3582</v>
       </c>
       <c r="S16" t="n">
-        <v>0.055</v>
+        <v>0.1912</v>
       </c>
       <c r="T16" t="n">
         <v>0.0617</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0067</v>
+        <v>0.1296</v>
       </c>
       <c r="V16" t="n">
         <v>1.1015</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. RIES</t>
+          <t>D. RODRIGUEZ GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3267</v>
+        <v>1.5503</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4322</v>
+        <v>-1.4233</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1055</v>
+        <v>2.9736</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4786</v>
+        <v>0.4081</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3931</v>
+        <v>2.236</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.8718</v>
+        <v>-1.8279</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2862</v>
+        <v>-0.7801</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8445</v>
+        <v>1.1535</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5583</v>
+        <v>-1.9335</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7648</v>
+        <v>1.1882</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5487</v>
+        <v>1.0825</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.3135</v>
+        <v>0.1056</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3881</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3582</v>
+        <v>2.5224</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1934</v>
+        <v>-1.407</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1077</v>
+        <v>-0.7924</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3011</v>
+        <v>-0.6146</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2239</v>
+        <v>2.9373</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2239</v>
+        <v>3.0597</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ GARCIA</t>
+          <t>J. RIES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1922</v>
+        <v>0.4423</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0239</v>
+        <v>0.6324</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2161</v>
+        <v>-0.1901</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4081</v>
+        <v>-1.4786</v>
       </c>
       <c r="H18" t="n">
-        <v>2.236</v>
+        <v>1.3931</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8279</v>
+        <v>-2.8718</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7801</v>
+        <v>0.2862</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1535</v>
+        <v>0.8445</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9335</v>
+        <v>-0.5583</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1882</v>
+        <v>-1.7648</v>
       </c>
       <c r="N18" t="n">
-        <v>1.0825</v>
+        <v>0.5487</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1056</v>
+        <v>-2.3135</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3881</v>
+        <v>0.3881</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5224</v>
+        <v>1.3582</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.7651</v>
+        <v>0.309</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.393</v>
+        <v>0.0925</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3721</v>
+        <v>0.2165</v>
       </c>
       <c r="V18" t="n">
-        <v>2.9373</v>
+        <v>1.2239</v>
       </c>
       <c r="W18" t="n">
-        <v>3.0597</v>
+        <v>1.2239</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1767</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="E19" t="n">
         <v>0.5311</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7077</v>
+        <v>-0.5987</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0951</v>
@@ -1936,13 +1936,13 @@
         <v>0.3881</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7517</v>
+        <v>-0.6427</v>
       </c>
       <c r="T19" t="n">
         <v>-0.424</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3277</v>
+        <v>-0.2187</v>
       </c>
       <c r="V19" t="n">
         <v>0.2821</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8835</v>
+        <v>-1.6833</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2119</v>
+        <v>-2.0117</v>
       </c>
       <c r="F20" t="n">
         <v>0.3284</v>
@@ -2014,10 +2014,10 @@
         <v>0.5821</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1335</v>
+        <v>0.0667</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3028</v>
+        <v>-0.1026</v>
       </c>
       <c r="U20" t="n">
         <v>0.1694</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Y. RODRÍGUEZ MACHÍN</t>
+          <t>A. JIMENEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3006</v>
+        <v>-3.7196</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9912</v>
+        <v>-1.5153</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3094</v>
+        <v>-2.2042</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9091</v>
+        <v>-1.2222</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8924</v>
+        <v>0.2743</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0167</v>
+        <v>-1.4965</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4001</v>
+        <v>-0.4426</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5447</v>
+        <v>0.103</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1446</v>
+        <v>-0.5455</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.509</v>
+        <v>-0.7796</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3477</v>
+        <v>0.1714</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1613</v>
+        <v>-0.951</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1642</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7463</v>
+        <v>0.3881</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4011</v>
+        <v>-0.6914</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3194</v>
+        <v>-0.1026</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9183</v>
+        <v>-0.5888</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.6283</v>
+        <v>-1.2239</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.6283</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. JIMENEZ FERNANDEZ</t>
+          <t>Y. RODRÍGUEZ MACHÍN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8653</v>
+        <v>-5.3143</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7155</v>
+        <v>-3.8931</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1497</v>
+        <v>-1.4212</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2222</v>
+        <v>-1.9091</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2743</v>
+        <v>-1.8924</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4965</v>
+        <v>-0.0167</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4426</v>
+        <v>-1.4001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.103</v>
+        <v>-1.5447</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5455</v>
+        <v>0.1446</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7796</v>
+        <v>-0.509</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1714</v>
+        <v>-0.3477</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.951</v>
+        <v>-0.1613</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5821</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3881</v>
+        <v>1.7463</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8371</v>
+        <v>-0.6127</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3028</v>
+        <v>0.4175</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5343</v>
+        <v>-1.0301</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2239</v>
+        <v>-1.6283</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2239</v>
+        <v>-1.6283</v>
       </c>
     </row>
     <row r="23">
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.873199999999999</v>
+        <v>7.208000000000001</v>
       </c>
       <c r="E23" t="n">
         <v>3.006700000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8668</v>
+        <v>4.201299999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>5.338699999999998</v>
+        <v>5.338699999999999</v>
       </c>
       <c r="H23" t="n">
         <v>6.6732</v>
@@ -2221,10 +2221,10 @@
         <v>-1.3346</v>
       </c>
       <c r="J23" t="n">
-        <v>7.385599999999999</v>
+        <v>7.385599999999998</v>
       </c>
       <c r="K23" t="n">
-        <v>3.131000000000001</v>
+        <v>3.131</v>
       </c>
       <c r="L23" t="n">
         <v>4.2549</v>
@@ -2239,7 +2239,7 @@
         <v>-5.5893</v>
       </c>
       <c r="P23" t="n">
-        <v>2.910599999999999</v>
+        <v>2.9106</v>
       </c>
       <c r="Q23" t="n">
         <v>-12.6123</v>
@@ -2248,22 +2248,22 @@
         <v>15.5226</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.611599999999999</v>
+        <v>-5.2771</v>
       </c>
       <c r="T23" t="n">
         <v>-1.7442</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.8672</v>
+        <v>-3.5326</v>
       </c>
       <c r="V23" t="n">
-        <v>4.235899999999999</v>
+        <v>4.2359</v>
       </c>
       <c r="W23" t="n">
         <v>9.977699999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-5.7417</v>
+        <v>-5.741700000000001</v>
       </c>
     </row>
   </sheetData>
